--- a/data/raw/maestro_productos.xlsx
+++ b/data/raw/maestro_productos.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +485,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Fecha_Alta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Activo</t>
         </is>
       </c>
@@ -530,7 +539,10 @@
       <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="b">
+      <c r="K2" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="L2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -579,7 +591,10 @@
       <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="b">
+      <c r="K3" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="L3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -628,7 +643,10 @@
       <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="b">
+      <c r="K4" s="2" t="n">
+        <v>45006</v>
+      </c>
+      <c r="L4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -677,7 +695,10 @@
       <c r="J5" t="n">
         <v>11</v>
       </c>
-      <c r="K5" t="b">
+      <c r="K5" s="2" t="n">
+        <v>45346</v>
+      </c>
+      <c r="L5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -726,7 +747,10 @@
       <c r="J6" t="n">
         <v>14</v>
       </c>
-      <c r="K6" t="b">
+      <c r="K6" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="L6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -775,7 +799,10 @@
       <c r="J7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="b">
+      <c r="K7" s="2" t="n">
+        <v>45698</v>
+      </c>
+      <c r="L7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -824,7 +851,10 @@
       <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="b">
+      <c r="K8" s="2" t="n">
+        <v>45573</v>
+      </c>
+      <c r="L8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -873,7 +903,10 @@
       <c r="J9" t="n">
         <v>9</v>
       </c>
-      <c r="K9" t="b">
+      <c r="K9" s="2" t="n">
+        <v>45415</v>
+      </c>
+      <c r="L9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -922,7 +955,10 @@
       <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" t="b">
+      <c r="K10" s="2" t="n">
+        <v>45684</v>
+      </c>
+      <c r="L10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -971,7 +1007,10 @@
       <c r="J11" t="n">
         <v>12</v>
       </c>
-      <c r="K11" t="b">
+      <c r="K11" s="2" t="n">
+        <v>45500</v>
+      </c>
+      <c r="L11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1020,7 +1059,10 @@
       <c r="J12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="b">
+      <c r="K12" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="L12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1069,7 +1111,10 @@
       <c r="J13" t="n">
         <v>11</v>
       </c>
-      <c r="K13" t="b">
+      <c r="K13" s="2" t="n">
+        <v>45283</v>
+      </c>
+      <c r="L13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1118,7 +1163,10 @@
       <c r="J14" t="n">
         <v>13</v>
       </c>
-      <c r="K14" t="b">
+      <c r="K14" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="L14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1167,7 +1215,10 @@
       <c r="J15" t="n">
         <v>7</v>
       </c>
-      <c r="K15" t="b">
+      <c r="K15" s="2" t="n">
+        <v>45160</v>
+      </c>
+      <c r="L15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1216,7 +1267,10 @@
       <c r="J16" t="n">
         <v>13</v>
       </c>
-      <c r="K16" t="b">
+      <c r="K16" s="2" t="n">
+        <v>45381</v>
+      </c>
+      <c r="L16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1265,7 +1319,10 @@
       <c r="J17" t="n">
         <v>5</v>
       </c>
-      <c r="K17" t="b">
+      <c r="K17" s="2" t="n">
+        <v>45161</v>
+      </c>
+      <c r="L17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1314,7 +1371,10 @@
       <c r="J18" t="n">
         <v>8</v>
       </c>
-      <c r="K18" t="b">
+      <c r="K18" s="2" t="n">
+        <v>45091</v>
+      </c>
+      <c r="L18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1363,7 +1423,10 @@
       <c r="J19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="b">
+      <c r="K19" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="L19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1412,7 +1475,10 @@
       <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="K20" t="b">
+      <c r="K20" s="2" t="n">
+        <v>45333</v>
+      </c>
+      <c r="L20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1461,7 +1527,10 @@
       <c r="J21" t="n">
         <v>13</v>
       </c>
-      <c r="K21" t="b">
+      <c r="K21" s="2" t="n">
+        <v>45771</v>
+      </c>
+      <c r="L21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1510,7 +1579,10 @@
       <c r="J22" t="n">
         <v>13</v>
       </c>
-      <c r="K22" t="b">
+      <c r="K22" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="L22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1559,7 +1631,10 @@
       <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="K23" t="b">
+      <c r="K23" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="L23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1608,7 +1683,10 @@
       <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="K24" t="b">
+      <c r="K24" s="2" t="n">
+        <v>45172</v>
+      </c>
+      <c r="L24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1657,7 +1735,10 @@
       <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="K25" t="b">
+      <c r="K25" s="2" t="n">
+        <v>45425</v>
+      </c>
+      <c r="L25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1706,7 +1787,10 @@
       <c r="J26" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="b">
+      <c r="K26" s="2" t="n">
+        <v>45097</v>
+      </c>
+      <c r="L26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1755,7 +1839,10 @@
       <c r="J27" t="n">
         <v>5</v>
       </c>
-      <c r="K27" t="b">
+      <c r="K27" s="2" t="n">
+        <v>45058</v>
+      </c>
+      <c r="L27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1804,7 +1891,10 @@
       <c r="J28" t="n">
         <v>12</v>
       </c>
-      <c r="K28" t="b">
+      <c r="K28" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="L28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1853,7 +1943,10 @@
       <c r="J29" t="n">
         <v>8</v>
       </c>
-      <c r="K29" t="b">
+      <c r="K29" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="L29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1902,7 +1995,10 @@
       <c r="J30" t="n">
         <v>5</v>
       </c>
-      <c r="K30" t="b">
+      <c r="K30" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="L30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1951,7 +2047,10 @@
       <c r="J31" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="b">
+      <c r="K31" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="L31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2000,7 +2099,10 @@
       <c r="J32" t="n">
         <v>4</v>
       </c>
-      <c r="K32" t="b">
+      <c r="K32" s="2" t="n">
+        <v>45100</v>
+      </c>
+      <c r="L32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2049,7 +2151,10 @@
       <c r="J33" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="b">
+      <c r="K33" s="2" t="n">
+        <v>45493</v>
+      </c>
+      <c r="L33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2098,7 +2203,10 @@
       <c r="J34" t="n">
         <v>13</v>
       </c>
-      <c r="K34" t="b">
+      <c r="K34" s="2" t="n">
+        <v>45618</v>
+      </c>
+      <c r="L34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2147,7 +2255,10 @@
       <c r="J35" t="n">
         <v>15</v>
       </c>
-      <c r="K35" t="b">
+      <c r="K35" s="2" t="n">
+        <v>45435</v>
+      </c>
+      <c r="L35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2196,7 +2307,10 @@
       <c r="J36" t="n">
         <v>4</v>
       </c>
-      <c r="K36" t="b">
+      <c r="K36" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="L36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2245,7 +2359,10 @@
       <c r="J37" t="n">
         <v>14</v>
       </c>
-      <c r="K37" t="b">
+      <c r="K37" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="L37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2294,7 +2411,10 @@
       <c r="J38" t="n">
         <v>11</v>
       </c>
-      <c r="K38" t="b">
+      <c r="K38" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="L38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2343,7 +2463,10 @@
       <c r="J39" t="n">
         <v>11</v>
       </c>
-      <c r="K39" t="b">
+      <c r="K39" s="2" t="n">
+        <v>45802</v>
+      </c>
+      <c r="L39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2392,7 +2515,10 @@
       <c r="J40" t="n">
         <v>13</v>
       </c>
-      <c r="K40" t="b">
+      <c r="K40" s="2" t="n">
+        <v>45685</v>
+      </c>
+      <c r="L40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2441,7 +2567,10 @@
       <c r="J41" t="n">
         <v>15</v>
       </c>
-      <c r="K41" t="b">
+      <c r="K41" s="2" t="n">
+        <v>45631</v>
+      </c>
+      <c r="L41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2490,7 +2619,10 @@
       <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="K42" t="b">
+      <c r="K42" s="2" t="n">
+        <v>45753</v>
+      </c>
+      <c r="L42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2539,7 +2671,10 @@
       <c r="J43" t="n">
         <v>12</v>
       </c>
-      <c r="K43" t="b">
+      <c r="K43" s="2" t="n">
+        <v>45348</v>
+      </c>
+      <c r="L43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2588,7 +2723,10 @@
       <c r="J44" t="n">
         <v>10</v>
       </c>
-      <c r="K44" t="b">
+      <c r="K44" s="2" t="n">
+        <v>45040</v>
+      </c>
+      <c r="L44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2637,7 +2775,10 @@
       <c r="J45" t="n">
         <v>4</v>
       </c>
-      <c r="K45" t="b">
+      <c r="K45" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="L45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2686,7 +2827,10 @@
       <c r="J46" t="n">
         <v>5</v>
       </c>
-      <c r="K46" t="b">
+      <c r="K46" s="2" t="n">
+        <v>44965</v>
+      </c>
+      <c r="L46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2735,7 +2879,10 @@
       <c r="J47" t="n">
         <v>11</v>
       </c>
-      <c r="K47" t="b">
+      <c r="K47" s="2" t="n">
+        <v>45088</v>
+      </c>
+      <c r="L47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2784,7 +2931,10 @@
       <c r="J48" t="n">
         <v>7</v>
       </c>
-      <c r="K48" t="b">
+      <c r="K48" s="2" t="n">
+        <v>45563</v>
+      </c>
+      <c r="L48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2833,7 +2983,10 @@
       <c r="J49" t="n">
         <v>6</v>
       </c>
-      <c r="K49" t="b">
+      <c r="K49" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="L49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2882,7 +3035,10 @@
       <c r="J50" t="n">
         <v>14</v>
       </c>
-      <c r="K50" t="b">
+      <c r="K50" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="L50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2931,7 +3087,10 @@
       <c r="J51" t="n">
         <v>10</v>
       </c>
-      <c r="K51" t="b">
+      <c r="K51" s="2" t="n">
+        <v>44945</v>
+      </c>
+      <c r="L51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2980,7 +3139,10 @@
       <c r="J52" t="n">
         <v>6</v>
       </c>
-      <c r="K52" t="b">
+      <c r="K52" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="L52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3029,7 +3191,10 @@
       <c r="J53" t="n">
         <v>4</v>
       </c>
-      <c r="K53" t="b">
+      <c r="K53" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="L53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3078,7 +3243,10 @@
       <c r="J54" t="n">
         <v>3</v>
       </c>
-      <c r="K54" t="b">
+      <c r="K54" s="2" t="n">
+        <v>45461</v>
+      </c>
+      <c r="L54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3127,7 +3295,10 @@
       <c r="J55" t="n">
         <v>6</v>
       </c>
-      <c r="K55" t="b">
+      <c r="K55" s="2" t="n">
+        <v>45322</v>
+      </c>
+      <c r="L55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3176,7 +3347,10 @@
       <c r="J56" t="n">
         <v>3</v>
       </c>
-      <c r="K56" t="b">
+      <c r="K56" s="2" t="n">
+        <v>45449</v>
+      </c>
+      <c r="L56" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3225,7 +3399,10 @@
       <c r="J57" t="n">
         <v>4</v>
       </c>
-      <c r="K57" t="b">
+      <c r="K57" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="L57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3274,7 +3451,10 @@
       <c r="J58" t="n">
         <v>7</v>
       </c>
-      <c r="K58" t="b">
+      <c r="K58" s="2" t="n">
+        <v>45041</v>
+      </c>
+      <c r="L58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3323,7 +3503,10 @@
       <c r="J59" t="n">
         <v>6</v>
       </c>
-      <c r="K59" t="b">
+      <c r="K59" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="L59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3372,7 +3555,10 @@
       <c r="J60" t="n">
         <v>8</v>
       </c>
-      <c r="K60" t="b">
+      <c r="K60" s="2" t="n">
+        <v>45825</v>
+      </c>
+      <c r="L60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3421,7 +3607,10 @@
       <c r="J61" t="n">
         <v>9</v>
       </c>
-      <c r="K61" t="b">
+      <c r="K61" s="2" t="n">
+        <v>45288</v>
+      </c>
+      <c r="L61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3470,7 +3659,10 @@
       <c r="J62" t="n">
         <v>14</v>
       </c>
-      <c r="K62" t="b">
+      <c r="K62" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="L62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3519,7 +3711,10 @@
       <c r="J63" t="n">
         <v>15</v>
       </c>
-      <c r="K63" t="b">
+      <c r="K63" s="2" t="n">
+        <v>45165</v>
+      </c>
+      <c r="L63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3568,7 +3763,10 @@
       <c r="J64" t="n">
         <v>6</v>
       </c>
-      <c r="K64" t="b">
+      <c r="K64" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="L64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3617,7 +3815,10 @@
       <c r="J65" t="n">
         <v>6</v>
       </c>
-      <c r="K65" t="b">
+      <c r="K65" s="2" t="n">
+        <v>45639</v>
+      </c>
+      <c r="L65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3666,7 +3867,10 @@
       <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="K66" t="b">
+      <c r="K66" s="2" t="n">
+        <v>45085</v>
+      </c>
+      <c r="L66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3715,7 +3919,10 @@
       <c r="J67" t="n">
         <v>5</v>
       </c>
-      <c r="K67" t="b">
+      <c r="K67" s="2" t="n">
+        <v>45068</v>
+      </c>
+      <c r="L67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3764,7 +3971,10 @@
       <c r="J68" t="n">
         <v>4</v>
       </c>
-      <c r="K68" t="b">
+      <c r="K68" s="2" t="n">
+        <v>45441</v>
+      </c>
+      <c r="L68" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3813,7 +4023,10 @@
       <c r="J69" t="n">
         <v>13</v>
       </c>
-      <c r="K69" t="b">
+      <c r="K69" s="2" t="n">
+        <v>45733</v>
+      </c>
+      <c r="L69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3862,7 +4075,10 @@
       <c r="J70" t="n">
         <v>4</v>
       </c>
-      <c r="K70" t="b">
+      <c r="K70" s="2" t="n">
+        <v>45704</v>
+      </c>
+      <c r="L70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3911,7 +4127,10 @@
       <c r="J71" t="n">
         <v>5</v>
       </c>
-      <c r="K71" t="b">
+      <c r="K71" s="2" t="n">
+        <v>45113</v>
+      </c>
+      <c r="L71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3960,7 +4179,10 @@
       <c r="J72" t="n">
         <v>7</v>
       </c>
-      <c r="K72" t="b">
+      <c r="K72" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="L72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4009,7 +4231,10 @@
       <c r="J73" t="n">
         <v>7</v>
       </c>
-      <c r="K73" t="b">
+      <c r="K73" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="L73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4058,7 +4283,10 @@
       <c r="J74" t="n">
         <v>14</v>
       </c>
-      <c r="K74" t="b">
+      <c r="K74" s="2" t="n">
+        <v>45396</v>
+      </c>
+      <c r="L74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4107,7 +4335,10 @@
       <c r="J75" t="n">
         <v>3</v>
       </c>
-      <c r="K75" t="b">
+      <c r="K75" s="2" t="n">
+        <v>45137</v>
+      </c>
+      <c r="L75" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4156,7 +4387,10 @@
       <c r="J76" t="n">
         <v>14</v>
       </c>
-      <c r="K76" t="b">
+      <c r="K76" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="L76" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4205,7 +4439,10 @@
       <c r="J77" t="n">
         <v>3</v>
       </c>
-      <c r="K77" t="b">
+      <c r="K77" s="2" t="n">
+        <v>45460</v>
+      </c>
+      <c r="L77" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4254,7 +4491,10 @@
       <c r="J78" t="n">
         <v>13</v>
       </c>
-      <c r="K78" t="b">
+      <c r="K78" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="L78" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4303,7 +4543,10 @@
       <c r="J79" t="n">
         <v>9</v>
       </c>
-      <c r="K79" t="b">
+      <c r="K79" s="2" t="n">
+        <v>45259</v>
+      </c>
+      <c r="L79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4352,7 +4595,10 @@
       <c r="J80" t="n">
         <v>12</v>
       </c>
-      <c r="K80" t="b">
+      <c r="K80" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="L80" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4401,7 +4647,10 @@
       <c r="J81" t="n">
         <v>7</v>
       </c>
-      <c r="K81" t="b">
+      <c r="K81" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="L81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4450,7 +4699,10 @@
       <c r="J82" t="n">
         <v>13</v>
       </c>
-      <c r="K82" t="b">
+      <c r="K82" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="L82" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4499,7 +4751,10 @@
       <c r="J83" t="n">
         <v>6</v>
       </c>
-      <c r="K83" t="b">
+      <c r="K83" s="2" t="n">
+        <v>45390</v>
+      </c>
+      <c r="L83" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4548,7 +4803,10 @@
       <c r="J84" t="n">
         <v>9</v>
       </c>
-      <c r="K84" t="b">
+      <c r="K84" s="2" t="n">
+        <v>45635</v>
+      </c>
+      <c r="L84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4597,7 +4855,10 @@
       <c r="J85" t="n">
         <v>13</v>
       </c>
-      <c r="K85" t="b">
+      <c r="K85" s="2" t="n">
+        <v>45086</v>
+      </c>
+      <c r="L85" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4646,7 +4907,10 @@
       <c r="J86" t="n">
         <v>11</v>
       </c>
-      <c r="K86" t="b">
+      <c r="K86" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="L86" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4695,7 +4959,10 @@
       <c r="J87" t="n">
         <v>5</v>
       </c>
-      <c r="K87" t="b">
+      <c r="K87" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="L87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4744,7 +5011,10 @@
       <c r="J88" t="n">
         <v>4</v>
       </c>
-      <c r="K88" t="b">
+      <c r="K88" s="2" t="n">
+        <v>45436</v>
+      </c>
+      <c r="L88" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4793,7 +5063,10 @@
       <c r="J89" t="n">
         <v>8</v>
       </c>
-      <c r="K89" t="b">
+      <c r="K89" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="L89" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4842,7 +5115,10 @@
       <c r="J90" t="n">
         <v>5</v>
       </c>
-      <c r="K90" t="b">
+      <c r="K90" s="2" t="n">
+        <v>45320</v>
+      </c>
+      <c r="L90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4891,7 +5167,10 @@
       <c r="J91" t="n">
         <v>13</v>
       </c>
-      <c r="K91" t="b">
+      <c r="K91" s="2" t="n">
+        <v>45395</v>
+      </c>
+      <c r="L91" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4940,7 +5219,10 @@
       <c r="J92" t="n">
         <v>5</v>
       </c>
-      <c r="K92" t="b">
+      <c r="K92" s="2" t="n">
+        <v>45229</v>
+      </c>
+      <c r="L92" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4989,7 +5271,10 @@
       <c r="J93" t="n">
         <v>4</v>
       </c>
-      <c r="K93" t="b">
+      <c r="K93" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="L93" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5038,7 +5323,10 @@
       <c r="J94" t="n">
         <v>14</v>
       </c>
-      <c r="K94" t="b">
+      <c r="K94" s="2" t="n">
+        <v>45234</v>
+      </c>
+      <c r="L94" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5087,7 +5375,10 @@
       <c r="J95" t="n">
         <v>7</v>
       </c>
-      <c r="K95" t="b">
+      <c r="K95" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5136,7 +5427,10 @@
       <c r="J96" t="n">
         <v>9</v>
       </c>
-      <c r="K96" t="b">
+      <c r="K96" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="L96" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5185,7 +5479,10 @@
       <c r="J97" t="n">
         <v>3</v>
       </c>
-      <c r="K97" t="b">
+      <c r="K97" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="L97" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5234,7 +5531,10 @@
       <c r="J98" t="n">
         <v>8</v>
       </c>
-      <c r="K98" t="b">
+      <c r="K98" s="2" t="n">
+        <v>45347</v>
+      </c>
+      <c r="L98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5283,7 +5583,10 @@
       <c r="J99" t="n">
         <v>13</v>
       </c>
-      <c r="K99" t="b">
+      <c r="K99" s="2" t="n">
+        <v>45684</v>
+      </c>
+      <c r="L99" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5332,7 +5635,10 @@
       <c r="J100" t="n">
         <v>11</v>
       </c>
-      <c r="K100" t="b">
+      <c r="K100" s="2" t="n">
+        <v>45051</v>
+      </c>
+      <c r="L100" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5381,7 +5687,10 @@
       <c r="J101" t="n">
         <v>4</v>
       </c>
-      <c r="K101" t="b">
+      <c r="K101" s="2" t="n">
+        <v>45083</v>
+      </c>
+      <c r="L101" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5430,7 +5739,10 @@
       <c r="J102" t="n">
         <v>14</v>
       </c>
-      <c r="K102" t="b">
+      <c r="K102" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="L102" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5479,7 +5791,10 @@
       <c r="J103" t="n">
         <v>3</v>
       </c>
-      <c r="K103" t="b">
+      <c r="K103" s="2" t="n">
+        <v>45146</v>
+      </c>
+      <c r="L103" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5528,7 +5843,10 @@
       <c r="J104" t="n">
         <v>8</v>
       </c>
-      <c r="K104" t="b">
+      <c r="K104" s="2" t="n">
+        <v>45176</v>
+      </c>
+      <c r="L104" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5577,7 +5895,10 @@
       <c r="J105" t="n">
         <v>8</v>
       </c>
-      <c r="K105" t="b">
+      <c r="K105" s="2" t="n">
+        <v>45004</v>
+      </c>
+      <c r="L105" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5626,7 +5947,10 @@
       <c r="J106" t="n">
         <v>13</v>
       </c>
-      <c r="K106" t="b">
+      <c r="K106" s="2" t="n">
+        <v>45068</v>
+      </c>
+      <c r="L106" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5675,7 +5999,10 @@
       <c r="J107" t="n">
         <v>13</v>
       </c>
-      <c r="K107" t="b">
+      <c r="K107" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="L107" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/maestro_productos.xlsx
+++ b/data/raw/maestro_productos.xlsx
@@ -540,7 +540,7 @@
         <v>12</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>45542</v>
+        <v>45545</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -592,7 +592,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>45597</v>
+        <v>45600</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45006</v>
+        <v>45009</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>45346</v>
+        <v>45349</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>45738</v>
+        <v>45741</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45698</v>
+        <v>45701</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -852,7 +852,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>45573</v>
+        <v>45576</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -904,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>45684</v>
+        <v>45687</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>12</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45500</v>
+        <v>45503</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>45850</v>
+        <v>45853</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>11</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>45283</v>
+        <v>45286</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>45728</v>
+        <v>45731</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>45160</v>
+        <v>45163</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>45381</v>
+        <v>45384</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1320,7 +1320,7 @@
         <v>5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>45161</v>
+        <v>45164</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>45091</v>
+        <v>45094</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>45904</v>
+        <v>45907</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>45333</v>
+        <v>45336</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>45771</v>
+        <v>45774</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1580,7 +1580,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>46039</v>
+        <v>46042</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         <v>15</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>45879</v>
+        <v>45882</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>13</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>45172</v>
+        <v>45175</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>9</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>45425</v>
+        <v>45428</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>45097</v>
+        <v>45100</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1840,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>45058</v>
+        <v>45061</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1892,7 +1892,7 @@
         <v>12</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>45456</v>
+        <v>45459</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>45677</v>
+        <v>45680</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>45813</v>
+        <v>45816</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>45100</v>
+        <v>45103</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -2152,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>45493</v>
+        <v>45496</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
@@ -2204,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -2256,7 +2256,7 @@
         <v>15</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>45435</v>
+        <v>45438</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -2308,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>45892</v>
+        <v>45895</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         <v>14</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>45938</v>
+        <v>45941</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -2412,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
@@ -2464,7 +2464,7 @@
         <v>11</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>45802</v>
+        <v>45805</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2516,7 +2516,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>45685</v>
+        <v>45688</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
@@ -2568,7 +2568,7 @@
         <v>15</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>45753</v>
+        <v>45756</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
@@ -2672,7 +2672,7 @@
         <v>12</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>45348</v>
+        <v>45351</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>45040</v>
+        <v>45043</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>45796</v>
+        <v>45799</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2828,7 +2828,7 @@
         <v>5</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>44965</v>
+        <v>44968</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2880,7 +2880,7 @@
         <v>11</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>45088</v>
+        <v>45091</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>7</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>45563</v>
+        <v>45566</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>45981</v>
+        <v>45984</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>14</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -3088,7 +3088,7 @@
         <v>10</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>44945</v>
+        <v>44948</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -3140,7 +3140,7 @@
         <v>6</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>45894</v>
+        <v>45897</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
@@ -3192,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>45710</v>
+        <v>45713</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -3244,7 +3244,7 @@
         <v>3</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>45461</v>
+        <v>45464</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -3296,7 +3296,7 @@
         <v>6</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>45322</v>
+        <v>45325</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         <v>3</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>45449</v>
+        <v>45452</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -3400,7 +3400,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
@@ -3452,7 +3452,7 @@
         <v>7</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>45041</v>
+        <v>45044</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>6</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>45240</v>
+        <v>45243</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -3556,7 +3556,7 @@
         <v>8</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>45825</v>
+        <v>45828</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>45288</v>
+        <v>45291</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>14</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>45314</v>
+        <v>45317</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -3712,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>45165</v>
+        <v>45168</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>45787</v>
+        <v>45790</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3816,7 +3816,7 @@
         <v>6</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>45639</v>
+        <v>45642</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>5</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>45085</v>
+        <v>45088</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>5</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>45068</v>
+        <v>45071</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
@@ -3972,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>45441</v>
+        <v>45444</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
@@ -4024,7 +4024,7 @@
         <v>13</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -4076,7 +4076,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>45704</v>
+        <v>45707</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -4128,7 +4128,7 @@
         <v>5</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>45113</v>
+        <v>45116</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -4180,7 +4180,7 @@
         <v>7</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>45800</v>
+        <v>45803</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>14</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>45396</v>
+        <v>45399</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>45137</v>
+        <v>45140</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         <v>14</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>45794</v>
+        <v>45797</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
@@ -4440,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>45460</v>
+        <v>45463</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -4492,7 +4492,7 @@
         <v>13</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>45783</v>
+        <v>45786</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -4544,7 +4544,7 @@
         <v>9</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>45259</v>
+        <v>45262</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -4596,7 +4596,7 @@
         <v>12</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>45881</v>
+        <v>45884</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -4648,7 +4648,7 @@
         <v>7</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>45794</v>
+        <v>45797</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -4700,7 +4700,7 @@
         <v>13</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>45856</v>
+        <v>45859</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -4752,7 +4752,7 @@
         <v>6</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>45390</v>
+        <v>45393</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -4804,7 +4804,7 @@
         <v>9</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
@@ -4856,7 +4856,7 @@
         <v>13</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>45086</v>
+        <v>45089</v>
       </c>
       <c r="L85" t="b">
         <v>1</v>
@@ -4908,7 +4908,7 @@
         <v>11</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="L86" t="b">
         <v>1</v>
@@ -4960,7 +4960,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>4</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>45838</v>
+        <v>45841</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         <v>5</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -5168,7 +5168,7 @@
         <v>13</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>45395</v>
+        <v>45398</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>5</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>45229</v>
+        <v>45232</v>
       </c>
       <c r="L92" t="b">
         <v>1</v>
@@ -5272,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>45238</v>
+        <v>45241</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45234</v>
+        <v>45237</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -5376,7 +5376,7 @@
         <v>7</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -5428,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>45895</v>
+        <v>45898</v>
       </c>
       <c r="L96" t="b">
         <v>1</v>
@@ -5480,7 +5480,7 @@
         <v>3</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>45964</v>
+        <v>45967</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
@@ -5532,7 +5532,7 @@
         <v>8</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>45347</v>
+        <v>45350</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -5584,7 +5584,7 @@
         <v>13</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>45684</v>
+        <v>45687</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -5636,7 +5636,7 @@
         <v>11</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>45051</v>
+        <v>45054</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -5688,7 +5688,7 @@
         <v>4</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>45083</v>
+        <v>45086</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -5740,7 +5740,7 @@
         <v>14</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>45998</v>
+        <v>46001</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -5792,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>45146</v>
+        <v>45149</v>
       </c>
       <c r="L103" t="b">
         <v>1</v>
@@ -5844,7 +5844,7 @@
         <v>8</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>45176</v>
+        <v>45179</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
@@ -5896,7 +5896,7 @@
         <v>8</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>45004</v>
+        <v>45007</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -5948,7 +5948,7 @@
         <v>13</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>45068</v>
+        <v>45071</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -6000,7 +6000,7 @@
         <v>13</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>46030</v>
+        <v>46033</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
